--- a/toutiao/toutiao.xlsx
+++ b/toutiao/toutiao.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -620,6 +620,646 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>菲林格尔股价创新高</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>/article/7552778026501653011/</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>每日经济新闻</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>21小时前</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>2025-09-23 11:11:16</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>标题直接提及股票价格，与A股市场相关</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>姚期智：量子人工智能亟待前瞻布局，培养尖端人才</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>/article/7552501209433735706/</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>上观新闻</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>前天19:22</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>2025-09-23 11:24:23</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>量子计算和人工智能是A股市场的重要科技板块，相关技术突破可能影响相关上市公司股价</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>潘功胜：境外机构熊猫债发行规模超过1万亿元</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>/article/7552827562676371978/</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>每日经济新闻</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>18小时前</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>2025-09-23 11:24:23</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>熊猫债发行规模涉及债券市场和外资流入，对A股市场资金面有间接影响</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>金融监管总局局长李云泽：5年来农信社改革蹄疾步稳 过半省份组建省级法人机构</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>/article/7552826911044174376/</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>中国网财经</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>18小时前</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>2025-09-23 11:24:23</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>农信社改革涉及金融体系改革，对银行板块和金融类上市公司有重要影响</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>有关预制菜，官方刚刚发声！</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>/article/7552834202815726106/</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>鲁网德州新闻中心</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>18小时前</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>2025-09-23 11:24:23</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>预制菜行业政策发声可能影响食品饮料板块相关上市公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>金融监管总局李云泽：监管质效持续提升 监管合力加快凝聚</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>/article/7552810523880931881/</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>同花顺财经</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>20小时前</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>2025-09-23 11:24:23</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>金融监管政策变化直接影响A股市场整体监管环境和金融机构</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>恶意挑动负面情绪，中央网信办严查这些行为！</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>/article/7552809368698307081/</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>法治甘肃网</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>20小时前</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>2025-09-23 11:28:54</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>网络监管政策可能影响市场情绪和互联网板块股价</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>AIGC海报：今年的制造业“500强”到底有多强？</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>/article/7552698081733706286/</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>华声在线</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>昨天08:06</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>2025-09-23 11:28:54</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>制造业龙头企业表现与相关板块股票走势密切相关</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>潘功胜：关于“十五五”及下一步金融改革的内容 将在中央统一部署后作进一步沟通</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>/article/7552807972532929051/</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>同花顺财经</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>20小时前</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>2025-09-23 11:28:54</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>央行行长关于金融改革的表态直接影响A股金融板块</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>潘功胜：“十四五”期间 实现了币值稳定和金融稳定双目标</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>/article/7552817233135731209/</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>每日经济新闻</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>19小时前</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>2025-09-23 11:28:54</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>央行货币政策与金融稳定直接影响A股市场整体表现</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>背靠英伟达，英维克股价涨超362%！AI算力狂飙带火液冷</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>/article/7552907244526977578/</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>澎湃新闻</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>13小时前</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>2025-09-23 11:28:54</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>直接涉及A股上市公司股价表现和AI概念板块</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>吴清：更好发挥中长期资金压舱石作用 吸引更多源头活水</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>/article/7552828795724595754/</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>每日经济新闻</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>18小时前</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>2025-09-23 11:30:46</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>证监会官员谈资金入市，直接涉及A股市场资金面</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>乳制品深加工研讨会在飞鹤智能工厂举办，中国乳业迎来“鲜活”时代</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>/article/7552787114681844259/</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>中国网财经</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>21小时前</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>2025-09-23 11:30:46</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>涉及乳制品行业和飞鹤公司，属于A股相关行业新闻</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>欧洲医药行业“风向标”开幕，儿童营养品牌inne频获德国药剂师专业认可</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>/article/7552387189418590720/</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>金融快报</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>前天12:02</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>2025-09-23 11:30:46</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>涉及医药健康行业，可能影响相关A股板块</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>突发！中菲在黄岩岛硬碰硬，马科斯不是傻，他是借中国之手办大事</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>/article/7550623282471387682/</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>垚瑞</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>7天前</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>2025-09-23 11:30:46</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>地缘政治事件可能影响市场情绪，间接影响A股</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>中设股份：股东陈凤军拟减持不超过1%公司股份</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>/article/7552881368426873359/</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>每日经济新闻</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>15小时前</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>2025-09-23 11:34:29</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>涉及A股上市公司股东减持行为</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2nm，大战打响</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>/article/7552387555405201972/</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>半导体行业观察</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>前天12:01</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>2025-09-23 11:34:29</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>半导体技术竞争可能影响相关A股科技板块</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>婴幼儿配方液态乳新规12月起施行</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>/article/7552683561292235315/</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>华商网</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>昨天07:09</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>2025-09-23 11:40:29</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>涉及乳制品行业政策，可能影响相关上市公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>奥美医疗：“注入AI芯片及人形智能机器人优质资产”传闻不属实</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>/article/7552809244353921582/</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>每日经济新闻</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>20小时前</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>2025-09-23 11:40:29</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>上市公司澄清公告直接影响股价</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>芯源微：前道化学清洗机签单表现优秀 新一代前道涂胶显影机预计Q4发机</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>/article/7552849682855133706/</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>每日经济新闻</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>17小时前</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>2025-09-23 11:40:29</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>半导体设备企业业务进展影响相关板块</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/toutiao/toutiao.xlsx
+++ b/toutiao/toutiao.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -55,11 +58,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F238"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,145 +467,137 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>21独家｜招商银行AIC最新进展：内聘已启动，争取年内成立</t>
+          <t>美股三大股指，齐创历史新高！牵手OpenAI，英伟达大涨近4%</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>/article/7552905212302787124/</t>
+          <t>/article/7553058037909537289/</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>21世纪经济报道</t>
+          <t>上观新闻</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>13小时前</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>2025-09-23 10:47:11</t>
-        </is>
+          <t>6小时前</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>45923.58371527777</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>招商银行是A股上市公司，其子公司进展可能影响股价</t>
+          <t>美股表现和英伟达股价变动对A股科技板块有重要影响</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>两连板德明利：控股股东、实际控制人李虎、田华本减持计划已实施完毕</t>
+          <t>证监会主席：关闭金交所、伪金交所进展明显，27家金交所已全部取消资质</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>/article/7552886507225219593/</t>
+          <t>/article/7552841630802346537/</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>每日经济新闻</t>
+          <t>大众新闻-大众日报</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>14小时前</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2025-09-23 10:47:11</t>
-        </is>
+          <t>20小时前</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>45923.58371527777</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>德明利是A股上市公司，大股东减持直接影响股票市场</t>
+          <t>证监会监管政策直接影响金融市场秩序和投资者信心</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>市场开始对碳化硅“刮目相看”</t>
+          <t>国家电投原董事长王炳华：降低工程造价是中国三代核电发展的最紧迫挑战</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>/article/7552824465509171746/</t>
+          <t>/article/7552903172907237940/</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>钛媒体APP</t>
+          <t>澎湃新闻</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>18小时前</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2025-09-23 10:47:11</t>
-        </is>
+          <t>16小时前</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>45923.58371527777</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>碳化硅是半导体材料，相关概念股可能受到市场关注影响</t>
+          <t>核电行业政策和发展趋势影响相关A股上市公司</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>近5成中国成人受失眠困扰，DORA新药能否引领百亿赛道？</t>
+          <t>首款元宇宙白酒上市，国台元宇宙·启元直播间半小时销售百万元</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>/article/7552923205086790178/</t>
+          <t>/article/7552841106988286510/</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>21世纪经济报道</t>
+          <t>澎湃新闻</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>12小时前</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>2025-09-23 10:50:10</t>
-        </is>
+          <t>20小时前</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>45923.58371527777</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>涉及医药行业及新药研发，可能影响相关A股医药企业</t>
+          <t>白酒行业创新和销售表现影响白酒板块上市公司股价</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>仰望U9X成就极速与圈速“双第一”</t>
+          <t>政策周历来了！这些政策与你有关——</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>/video/7552824697017139753/</t>
+          <t>/article/7552876549880545842/</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>大象新闻</t>
+          <t>首都之窗</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -609,654 +605,6972 @@
           <t>18小时前</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>2025-09-23 10:50:10</t>
-        </is>
+      <c r="E6" s="2" t="n">
+        <v>45923.58371527777</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>若涉及新能源汽车企业可能影响相关A股板块</t>
+          <t>政策发布可能涉及经济、产业等多方面，对A股市场有广泛影响</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>菲林格尔股价创新高</t>
+          <t>中国东方资产管理股份有限公司广东省分公司    债权催收暨招商公告</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>/article/7552778026501653011/</t>
+          <t>/article/7553070392614355495/</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>每日经济新闻</t>
+          <t>南方日报</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>21小时前</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>2025-09-23 11:11:16</t>
-        </is>
+          <t>6小时前</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>45923.59795138889</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>标题直接提及股票价格，与A股市场相关</t>
+          <t>涉及资产管理公司业务，可能与金融板块相关</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>姚期智：量子人工智能亟待前瞻布局，培养尖端人才</t>
+          <t>中科海讯：与北部湾港集团签订战略合作协议</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>/article/7552501209433735706/</t>
+          <t>/article/7552873654850388530/</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>上观新闻</t>
+          <t>每日经济新闻</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>前天19:22</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>2025-09-23 11:24:23</t>
-        </is>
+          <t>19小时前</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>45923.6066087963</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>量子计算和人工智能是A股市场的重要科技板块，相关技术突破可能影响相关上市公司股价</t>
+          <t>涉及上市公司中科海讯的战略合作，属于A股相关公司动态</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>潘功胜：境外机构熊猫债发行规模超过1万亿元</t>
+          <t>我国迎来第八个中国农民丰收节</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>/article/7552827562676371978/</t>
+          <t>/article/7553070851482976794/</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>每日经济新闻</t>
+          <t>天下泉城</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>18小时前</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>2025-09-23 11:24:23</t>
-        </is>
+          <t>6小时前</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>45923.60907407408</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>熊猫债发行规模涉及债券市场和外资流入，对A股市场资金面有间接影响</t>
+          <t>农业相关节日，可能影响农业板块股票</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>金融监管总局局长李云泽：5年来农信社改革蹄疾步稳 过半省份组建省级法人机构</t>
+          <t>2025国庆档电影片单发布</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>/article/7552826911044174376/</t>
+          <t>/article/7552832195090547254/</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>中国网财经</t>
+          <t>汉水襄阳</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>18小时前</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>2025-09-23 11:24:23</t>
-        </is>
+          <t>21小时前</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>45923.60907407408</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>农信社改革涉及金融体系改革，对银行板块和金融类上市公司有重要影响</t>
+          <t>影视娱乐行业新闻，与A股传媒板块相关</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>有关预制菜，官方刚刚发声！</t>
+          <t>第三届中国猕猴桃博览会成果丰硕</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>/article/7552834202815726106/</t>
+          <t>/article/7553062520995545643/</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>鲁网德州新闻中心</t>
+          <t>华商网</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>18小时前</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>2025-09-23 11:24:23</t>
-        </is>
+          <t>6小时前</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>45923.60907407408</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>预制菜行业政策发声可能影响食品饮料板块相关上市公司</t>
+          <t>农业展会成果，可能影响农业相关股票</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>金融监管总局李云泽：监管质效持续提升 监管合力加快凝聚</t>
+          <t>第四期：金融赋能军工产业 特色服务筑牢强军根基</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>/article/7552810523880931881/</t>
+          <t>/article/7553094853135991336/</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>同花顺财经</t>
+          <t>中国网财经</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>20小时前</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>2025-09-23 11:24:23</t>
-        </is>
+          <t>4小时前</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>45923.60907407408</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>金融监管政策变化直接影响A股市场整体监管环境和金融机构</t>
+          <t>金融与军工产业结合，与A股军工和金融板块相关</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>恶意挑动负面情绪，中央网信办严查这些行为！</t>
+          <t>中信银行积极开展2025年国家网络安全宣传周活动</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>/article/7552809368698307081/</t>
+          <t>/article/7553097879242490406/</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>法治甘肃网</t>
+          <t>青新财经</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>20小时前</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>2025-09-23 11:28:54</t>
-        </is>
+          <t>4小时前</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>45923.61892361111</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>网络监管政策可能影响市场情绪和互联网板块股价</t>
+          <t>中信银行是A股上市公司，其相关活动可能对股价产生影响</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AIGC海报：今年的制造业“500强”到底有多强？</t>
+          <t>20cm速递｜外资看好中国储能发展，创业板新能源ETF华夏（159368）涨超2%，同类规模第一</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>/article/7552698081733706286/</t>
+          <t>/article/7553098051947250215/</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>华声在线</t>
+          <t>每日经济新闻</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>昨天08:06</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>2025-09-23 11:28:54</t>
-        </is>
+          <t>4小时前</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>45923.61892361111</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>制造业龙头企业表现与相关板块股票走势密切相关</t>
+          <t>直接涉及创业板ETF和新能源板块，与A股市场高度相关</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>潘功胜：关于“十五五”及下一步金融改革的内容 将在中央统一部署后作进一步沟通</t>
+          <t>省药品监管局召开药品零售连锁企业集体约谈会</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>/article/7552807972532929051/</t>
+          <t>/article/7552813125864358435/</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>同花顺财经</t>
+          <t>青海法治报</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>20小时前</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>2025-09-23 11:28:54</t>
-        </is>
+          <t>23小时前</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>45923.63251157408</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>央行行长关于金融改革的表态直接影响A股金融板块</t>
+          <t>药品监管政策可能影响医药零售类上市公司</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>潘功胜：“十四五”期间 实现了币值稳定和金融稳定双目标</t>
+          <t>知名品牌停牌！曾半年闭店近千家，很多人都买过→</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>/article/7552817233135731209/</t>
+          <t>/article/7552916959164187151/</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>每日经济新闻</t>
+          <t>汉水襄阳</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>19小时前</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>2025-09-23 11:28:54</t>
-        </is>
+          <t>10小时前</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>45923.63251157408</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>央行货币政策与金融稳定直接影响A股市场整体表现</t>
+          <t>涉及上市公司停牌信息，直接影响股票交易</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>背靠英伟达，英维克股价涨超362%！AI算力狂飙带火液冷</t>
+          <t>商务部电子商务司负责人介绍2025年1-8月我国电子商务发展情况</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>/article/7552907244526977578/</t>
+          <t>/article/7552826828214288923/</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>澎湃新闻</t>
+          <t>商务微新闻</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>13小时前</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>2025-09-23 11:28:54</t>
-        </is>
+          <t>22小时前</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>45923.63251157408</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>直接涉及A股上市公司股价表现和AI概念板块</t>
+          <t>电商行业数据发布，影响电商类上市公司股价</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>吴清：更好发挥中长期资金压舱石作用 吸引更多源头活水</t>
+          <t>低空经济能直接适用航路概念吗？</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>/article/7552828795724595754/</t>
+          <t>/article/7553061356011323956/</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>每日经济新闻</t>
+          <t>澎湃新闻</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>18小时前</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>2025-09-23 11:30:46</t>
-        </is>
+          <t>7小时前</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>45923.63251157408</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>证监会官员谈资金入市，直接涉及A股市场资金面</t>
+          <t>低空经济政策讨论，涉及相关概念股</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>乳制品深加工研讨会在飞鹤智能工厂举办，中国乳业迎来“鲜活”时代</t>
+          <t>特斯拉全球首座完整V4超级充电站落地美国加州坎贝尔市</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>/article/7552787114681844259/</t>
+          <t>/article/7553125247684313635/</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>中国网财经</t>
+          <t>环球Tech</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>21小时前</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>2025-09-23 11:30:46</t>
-        </is>
+          <t>3小时前</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>45923.63251157408</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>涉及乳制品行业和飞鹤公司，属于A股相关行业新闻</t>
+          <t>特斯拉相关新闻，影响新能源汽车产业链股票</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>欧洲医药行业“风向标”开幕，儿童营养品牌inne频获德国药剂师专业认可</t>
+          <t>中日钓鱼岛战争谁会赢？美国兵推结果出炉，美媒：日本大概率胜出</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>/article/7552387189418590720/</t>
+          <t>/article/7552902814662427177/</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>金融快报</t>
+          <t>卿羽飞</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>前天12:02</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>2025-09-23 11:30:46</t>
-        </is>
+          <t>10小时前</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>45923.63251157408</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>涉及医药健康行业，可能影响相关A股板块</t>
+          <t>地缘政治风险可能影响军工、国防相关股票</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>突发！中菲在黄岩岛硬碰硬，马科斯不是傻，他是借中国之手办大事</t>
+          <t>闽人新智丨福建首条“冰上丝绸之路”航线启航</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>/article/7550623282471387682/</t>
+          <t>/article/7553108201047196196/</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>垚瑞</t>
+          <t>东南网</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>7天前</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>2025-09-23 11:30:46</t>
-        </is>
+          <t>4小时前</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>45923.63959490741</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>地缘政治事件可能影响市场情绪，间接影响A股</t>
+          <t>航运航线开通，可能影响A股港口航运板块</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>中设股份：股东陈凤军拟减持不超过1%公司股份</t>
+          <t>始祖鸟烟花秀“炸山”，ESG究竟营销卖点还是企业价值观？</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>/article/7552881368426873359/</t>
+          <t>/article/7552869358256374322/</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>每日经济新闻</t>
+          <t>陆家嘴金融网</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>15小时前</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>2025-09-23 11:34:29</t>
-        </is>
+          <t>20小时前</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>45923.64653935185</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>涉及A股上市公司股东减持行为</t>
+          <t>涉及ESG（环境、社会和治理）概念，这是A股市场关注的投资主题和上市公司评级标准</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2nm，大战打响</t>
+          <t>教育部：推进人才供需适配改革 学科专业目录从10年一修订到每年更新</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>/article/7552387555405201972/</t>
+          <t>/article/7553104310830236202/</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>半导体行业观察</t>
+          <t>大象新闻</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>前天12:01</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>2025-09-23 11:34:29</t>
-        </is>
+          <t>5小时前</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>45923.64653935185</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>半导体技术竞争可能影响相关A股科技板块</t>
+          <t>教育改革政策影响教育类上市公司和人力资源服务板块</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>婴幼儿配方液态乳新规12月起施行</t>
+          <t>湖南省推动工业母机与轨道交通产业深度融合</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>/article/7552683561292235315/</t>
+          <t>/article/7553048387805774382/</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>华商网</t>
+          <t>华声在线</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>昨天07:09</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>2025-09-23 11:40:29</t>
-        </is>
+          <t>8小时前</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>45923.64653935185</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>涉及乳制品行业政策，可能影响相关上市公司</t>
+          <t>工业母机（机床）和轨道交通都是A股重要产业板块，政策推动直接影响相关上市公司</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>奥美医疗：“注入AI芯片及人形智能机器人优质资产”传闻不属实</t>
+          <t>文化和旅游部通报第五批次文化和旅游领域暗访情况</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>/article/7552809244353921582/</t>
+          <t>/article/7553099599972483636/</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>每日经济新闻</t>
+          <t>东南网</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>20小时前</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>2025-09-23 11:40:29</t>
-        </is>
+          <t>5小时前</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>45923.64653935185</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>上市公司澄清公告直接影响股价</t>
+          <t>文旅行业监管通报影响A股旅游、酒店、文化传媒类上市公司</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>芯源微：前道化学清洗机签单表现优秀 新一代前道涂胶显影机预计Q4发机</t>
+          <t>国家体育总局印发《关于推动运动促进健康事业高质量发展的指导意见》</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>/article/7552849682855133706/</t>
+          <t>/article/7552847275714707977/</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
+          <t>澎湃新闻</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>21小时前</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>45923.64653935185</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>体育产业政策利好A股体育用品、健康服务等相关上市公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>从福建跨省履新的张文东，有新职！在市场监管总局工作多年的刘健男，已任新职！</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>/article/7552467434754540042/</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>鲁网潍坊</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>10小时前</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="n">
+        <v>45923.64653935185</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>市场监管总局人事变动可能影响监管政策，对A股整体市场环境有影响</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>博纳影业：中信证券投资有限公司等持股比例已降至8.90%</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>/article/7552854086316524058/</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
           <t>每日经济新闻</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>21小时前</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>45923.65351851852</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>涉及上市公司股东变动，与A股直接相关</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>又一安徽企业冲刺A+H上市！涉及半导体领域→</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>/article/7553085407769690664/</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>连接徽商</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>6小时前</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="n">
+        <v>45923.65351851852</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>企业IPO动态，直接影响A股市场</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>科思科技与中机应急签署战略合作协议</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>/article/7553094174325735977/</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>每日经济新闻</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>5小时前</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="n">
+        <v>45923.65351851852</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>上市公司业务合作，与A股相关</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>18天直达欧洲！全球首条中欧北极集装箱快航正式通航</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>/article/7553064219835384358/</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>上观新闻</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>8小时前</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="n">
+        <v>45923.66048611111</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>航运物流重大进展，利好A股航运、港口、物流等相关板块</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>“十四五”期间房地产融资协调机制支持近2000万套住房建设交付</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>/article/7552878416232514083/</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>华声在线</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>20小时前</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="n">
+        <v>45923.66048611111</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>房地产政策重大利好，直接影响A股房地产板块及相关产业链</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>【速看】一汽解放传来好消息</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>/article/7552845092151624201/</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>吉林之声</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>22小时前</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="n">
+        <v>45923.66048611111</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>汽车制造业重要消息，直接影响A股汽车制造板块及相关上市公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>最新一批国家药品集采，来了→</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>/article/7552926747461681679/</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>汉水襄阳</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>9小时前</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="n">
+        <v>45923.66743055556</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>药品集采政策直接影响医药上市公司业绩和股价，与A股医药板块高度相关</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>宾利重启纯燃油车型开发，放弃2035年全面电动化目标</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>/article/7553122635949883943/</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>环球Tech</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>4小时前</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="n">
+        <v>45923.67435185185</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>汽车行业政策变化可能影响汽车产业链相关上市公司股价</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>不止信贷！绿色金融新十年，数字技术成关键变量</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>/article/7552876094207115785/</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>21号骑象人</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>20小时前</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="n">
+        <v>45923.67435185185</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>绿色金融政策可能影响银行、环保等相关板块上市公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>这场全国大赛榜单揭晓！山东港口青岛港一举斩获两项大奖</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>/article/7552830062727365120/</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>大众新闻•半岛都市报</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>23小时前</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="n">
+        <v>45923.67435185185</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>港口行业荣誉可能影响港口物流板块相关上市公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>科创债ETF天弘（159111）明日上市，可T+0现金申赎，机构：短期建议关注科创债主题性机会</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>/article/7553106149357191680/</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>21世纪经济报道</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>5小时前</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="n">
+        <v>45923.67435185185</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>ETF基金上市交易直接涉及证券市场投资品种</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>中国稀土钨条交易迷局</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>/article/7552914419575996968/</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>每日经济新闻</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>18小时前</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="n">
+        <v>45923.67435185185</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>稀土交易情况直接影响稀土永磁等资源类上市公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>中国加快制定国家标准 推动预制菜走向“明白菜”</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>/article/7553091646197187126/</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>济南日报·爱济南</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>6小时前</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="n">
+        <v>45923.68135416666</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>预制菜行业标准可能影响相关上市公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>国际油价窄幅震荡，美油主力合约收跌0.1%</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>/article/7553036606777639443/</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>每日经济新闻</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>10小时前</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="n">
+        <v>45923.68135416666</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>国际油价波动可能影响A股能源板块</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>毕业季特惠、学生分期免息、先签约后补手续——部分医美机构瞄上这些“优质客户”</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>/article/7553115590102221354/</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>环球健康</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>5小时前</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="n">
+        <v>45923.68135416666</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>医美行业动态可能涉及相关上市公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>英伟达官宣向OpenAI投资1000亿！用至少400万GPU打造超级AI巨兽</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>/article/7553109518264058407/</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>机器之心Pro</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>5小时前</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="n">
+        <v>45923.68832175926</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>涉及英伟达重大投资可能影响AI产业链相关A股公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>“西贝采购总监要求退回供应商所有预制产品”？回应：不属实</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>/article/7553065636864328218/</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>大象新闻</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>8小时前</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="n">
+        <v>45923.69518518518</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>涉及餐饮企业西贝的供应链消息，可能影响相关食品饮料板块上市公司股价</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>“9・24 行情”一周年：主动权益基金 “翻倍基”批量涌现，长期配置逻辑成关键</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>/article/7553151923893961226/</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>每日经济新闻</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>3小时前</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="n">
+        <v>45923.69518518518</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>直接讨论基金市场和A股行情表现，与A股市场高度相关</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>国庆“拼好团”打卡神州四极：美团旅行“国门景区”热度增40% ，新疆、黑龙江、云南居前三</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>/article/7552909982715462183/</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>随申Hi</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>18小时前</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="n">
+        <v>45923.69518518518</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>涉及旅游消费数据，可能影响旅游、酒店、航空等A股相关板块</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>“火腿大王”拟投资不超过3亿元，跨界这一行业！股价“一字涨停”</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>/article/7553101976695783962/</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>每日经济新闻</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>6小时前</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="n">
+        <v>45923.70209490741</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>涉及上市公司投资行为及股价变动，与A股直接相关</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>证监会党委：协同各方持续推动各类中长期资金入市和占比提升 加强战略性力量储备和稳市机制建设</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>/article/7552864361522397736/</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>每日经济新闻</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>21小时前</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="n">
+        <v>45923.70209490741</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>证监会发布的市场政策指引，直接影响A股市场资金面和稳定机制</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>辉瑞73亿美元收购生物科技公司Metsera 布局千亿减肥药市场</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>/article/7553125249303216655/</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>环球Tech</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>5小时前</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="n">
+        <v>45923.70209490741</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>跨国医药巨头并购交易，可能影响A股相关医药板块和概念股</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>欧债收益率多数上涨，法国10年期国债收益率涨0.6个基点</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>/article/7553039260434072074/</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>每日经济新闻</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>10小时前</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="n">
+        <v>45923.70907407408</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>欧洲债市波动可能间接影响A股市场情绪</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>18天直达欧洲！全球首条中欧北极集装箱快航正式通航</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>/article/7553099592083046938/</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>东南网</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>6小时前</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="n">
+        <v>45923.70907407408</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>国际物流新航线可能影响外贸及航运类A股企业</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>宝马新产品开发战略公布</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>/article/7553114370142880292/</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>大象新闻</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>6小时前</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="n">
+        <v>45923.71599537037</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>宝马作为汽车行业重要企业，其新产品战略可能影响汽车产业链相关A股上市公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>秋分·钓鱼经济“钓”动市场新活力｜财经二十四节气</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>/article/7553085556771586598/</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>21世纪经济报道</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>8小时前</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="n">
+        <v>45923.71599537037</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>财经类报道，涉及市场活力，可能与消费类、休闲产业A股相关</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>促进卫生健康领域科技创新发展！云南出台20条措施→</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>/article/7552918523064975906/</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>掌上曲靖</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>18小时前</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="n">
+        <v>45923.71599537037</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>地方政策支持医疗科技创新，可能利好相关医药生物A股</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>贵研铂业抛近13亿元定增预案，发力贵金属材料研发与资源循环利用</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>/article/7552907398639108659/</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>每日经济新闻</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>19小时前</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="n">
+        <v>45923.7229050926</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>贵研铂业是A股上市公司（股票代码600459），定增事项直接影响股价</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>银行板块领涨，估值处于历史低位，政策面持续释放积极信号</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>/article/7553115325189898794/</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>每日经济新闻</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>6小时前</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="n">
+        <v>45923.72982638889</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>直接涉及银行板块股市表现和估值</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>银行间主要利率债收益率盘初普遍上行</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>/article/7553081010133467684/</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>每日经济新闻</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>8小时前</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="n">
+        <v>45923.72982638889</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>利率债收益率变化直接影响债券市场和银行股表现</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>从药柜到妆台！这家山东药企“破圈”玩转中药护肤</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>/article/7553123223930094090/</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>大象新闻</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>6小时前</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="n">
+        <v>45923.75074074074</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>涉及药企业务转型，可能对相关上市公司股价产生影响</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>监管部门发布节日价格提醒倡议</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>/article/7553099581119070756/</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>东南网</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>7小时前</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="n">
+        <v>45923.75074074074</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>监管政策可能影响消费类上市公司经营和股价</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>数览成绩单丨跻身全球前十！中国创新跑出“加速度”</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>/article/7553071567211659839/</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>华声在线</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>9小时前</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="n">
+        <v>45923.75074074074</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>创新产业发展情况可能影响科技类上市公司估值</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>最高给予6万元生活补助，湖南18家省属国企组团揽才</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>/article/7553122038454501930/</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>三湘都市报</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>6小时前</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="n">
+        <v>45923.75074074074</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>国企人才政策可能影响相关上市国企的人力资源成本和竞争力</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>西贝投资成立饭积极餐饮管理公司</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>/article/7553168930760688179/</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>每日经济新闻</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>3小时前</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="n">
+        <v>45923.75730324074</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>涉及餐饮企业投资设立新公司，可能影响相关餐饮类上市公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>鲁医健康说·秋季健康与疾病防治｜流感疫苗哪些人应优先接种、什么时间接种、如何预约？一篇文章说清楚！</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>/article/7552898380788236835/</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>大众新闻-大众日报</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>21小时前</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="n">
+        <v>45923.75730324074</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>涉及疫苗相关内容，与医药生物类上市公司相关</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>雷军：小米每次进步都是被挑战逼的 关键改变在2020年</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>/article/7553091987743687214/</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>CNMO科技</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>8小时前</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="n">
+        <v>45923.75730324074</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>涉及小米公司，作为港股上市公司对A股科技板块有影响</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>英伟达将向OpenAI投资千亿美元共建数据中心</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>/article/7553040453180932660/</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>上观新闻</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>12小时前</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="n">
+        <v>45923.76456018518</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>涉及AI巨头投资合作，可能影响A股相关科技板块</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>天融信：暂未参与昇腾384超节点的供应链</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>/article/7553132091626488366/</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>每日经济新闻</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>6小时前</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="n">
+        <v>45923.76456018518</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>上市公司天融信发布业务说明，直接影响股价表现</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>白酒“双节”行情旺季不旺？终端以价换量，茅台动销有所回暖</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>/article/7553107101766435367/</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>济南日报·爱济南</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>7小时前</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="n">
+        <v>45923.76456018518</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>涉及白酒行业和茅台等上市公司经营情况，直接影响A股消费板块</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>国家体育总局印发《关于推动运动促进健康事业高质量发展的指导意见》</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>/article/7552872559650423350/</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>河南日报</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>22小时前</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="n">
+        <v>45923.76456018518</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>政策文件可能利好A股体育产业相关上市公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>深夜大涨！黄金、英伟达、苹果、特斯拉……</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>/article/7553135067489501742/</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>济南日报·爱济南</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>6小时前</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="n">
+        <v>45923.77151620371</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>涉及美股和黄金市场表现，对A股相关板块有间接影响</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>财经聚焦丨今年中国农民丰收节金秋消费季，有何新看点？</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>/article/7553099531929076243/</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>东南网</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>8小时前</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="n">
+        <v>45923.77151620371</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>消费季活动可能影响消费类上市公司业绩，与A股消费板块相关</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>改革重组激发澎湃动能：贵州大数据集团“数”径通达，引领数据价值释放</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>/article/7552919204695720482/</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>澎湃新闻</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>20小时前</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="n">
+        <v>45923.77151620371</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>大数据产业发展和国企改革可能影响相关科技类上市公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>“9・24行情”一周年：A股新开户将超3000万户，头部券商抢客忙，ETF成资金入市新通道</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>/article/7553099436960891392/</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>每日经济新闻</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>8小时前</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="n">
+        <v>45923.77846064815</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>直接涉及A股市场开户数据、券商业务和资金入市渠道，与A股高度相关</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>投资银条卖爆了，银价为何暴涨？</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>/article/7552913444626842155/</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>青岛日报</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>20小时前</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="n">
+        <v>45923.77846064815</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>涉及贵金属投资和价格波动，与A股市场的有色金属板块和投资品种相关</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>20cm速递｜尾盘拉升，创业板新能源ETF华夏（159368）收涨1.93%，同类规模第一</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>/article/7553187496495858214/</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>每日经济新闻</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>3小时前</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="n">
+        <v>45923.79233796296</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>涉及创业板ETF及新能源板块，与A股直接相关</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>英伟达将向OpenAI投资千亿美元共建数据中心</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>/article/7553181966192706084/</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>济南日报·爱济南</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>3小时前</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="n">
+        <v>45923.7993287037</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>涉及科技巨头重大投资，可能影响相关A股板块</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>刘强东“10年1元年薪”之约到期，未来薪资如何安排待解</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>/article/7553141889441792553/</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>济南日报·爱济南</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>6小时前</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="n">
+        <v>45923.7993287037</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>涉及上市公司高管薪酬安排，与A股上市公司治理相关</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>大股东阿里拟减持苏宁易购股份不超2.85%：基于自身商业安排</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>/article/7553105765465113140/</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>大众新闻•半岛都市报</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>9小时前</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="n">
+        <v>45923.81317129629</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>上市公司重要股东减持可能影响A股相关个股</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>工信部：“十五五”时期开辟人形机器人、脑机接口、元宇宙、量子信息等新赛道 创建一批未来产业先导区</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>/article/7553113787826455059/</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>每日经济新闻</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>8小时前</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="n">
+        <v>45923.81990740741</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>涉及新兴产业政策，可能影响相关A股上市公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>今创集团助力首列中国标准智能市域列车</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>/article/7553098896688366126/</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>常州网</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>9小时前</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="n">
+        <v>45923.81990740741</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>今创集团为A股上市公司，涉及公司业务进展</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>任正非：汽车行业的根本是要把车造好，车的最高级别就是安全</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>/article/7553170787407020596/</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>政知新媒体</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>5小时前</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="n">
+        <v>45923.82706018518</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>涉及汽车行业观点，可能影响汽车板块股价</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>金融ETF（510230）午前翻红，涨超0.5%！机构：银行中期分红助力板块估值修复</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>/article/7553123058559517227/</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>每日经济新闻</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>8小时前</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="n">
+        <v>45923.83400462963</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>直接涉及A股金融板块及ETF产品</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>高盛刘劲津答21：海外中长线投资者对中国市场兴趣非常高</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>/article/7552902594885141044/</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>21世纪经济报道</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>22小时前</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="n">
+        <v>45923.84104166667</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>涉及中国资本市场投资动向，与A股相关</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>中证A500指数发布一周年，A500ETF基金（512050）助力布局A股核心资产</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>/article/7553091644443132431/</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>每日经济新闻</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>10小时前</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="n">
+        <v>45923.8475925926</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>标题直接提及A股核心资产及相关ETF基金</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>中证1000股指期货（IM）主力合约向下触及7000点</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>/article/7553164854316597775/</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>每日经济新闻</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>6小时前</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="n">
+        <v>45923.8475925926</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>涉及A股衍生品市场动态</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>“火腿第一股”涨停！多次投资失败后跨界芯片，公司回应</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>/article/7553124151238623787/</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>21世纪经济报道</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>8小时前</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="n">
+        <v>45923.85454861111</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>明确提及A股上市公司股价变动和业务转型</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>疯狂建算力！英伟达计划最高投资OpenAI1000亿美元</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>/article/7553113867077927466/</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>21世纪经济报道</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>9小时前</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="n">
+        <v>45923.86148148148</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>英伟达是科技巨头，其投资动向可能影响A股相关科技板块</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>国家能源局：1-8月全社会用电量累计68788亿千瓦时，同比增长4.6%</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>/article/7553176680739914286/</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>每日经济新闻</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>5小时前</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="n">
+        <v>45923.86148148148</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>宏观经济数据可能影响能源及工业板块走势</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>21社论丨金融服务实体经济质效齐升，积极助力高质量发展</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>/article/7553050424115331618/</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>21世纪经济报道</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>13小时前</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="n">
+        <v>45923.86871527778</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>涉及金融服务实体经济主题，与A股金融市场相关</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>白酒“双节”行情旺季不旺？终端以价换量，茅台动销有所回暖</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>/article/7553063104210076214/</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>澎湃新闻</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>13小时前</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="n">
+        <v>45923.88960648148</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>白酒行业动态直接影响相关A股上市公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>军工投资的中流砥柱，航空航天ETF（159227）规模创新高，航宇科技领涨</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>/article/7553163506250416659/</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>每日经济新闻</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>7小时前</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="n">
+        <v>45923.89663194444</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>涉及ETF基金和上市公司股价表现，与A股直接相关</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>汉得信息：公司和甲骨文有合作</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>/article/7553086213297537545/</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>每日经济新闻</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>12小时前</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="n">
+        <v>45923.89663194444</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>汉得信息为A股上市公司，公司合作消息可能影响股价</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>18天直达欧洲！全球首条中欧北极集装箱快航正式通航</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>/article/7553072811397399066/</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>华商网</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>13小时前</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="n">
+        <v>45923.91048611111</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>涉及国际航运和贸易，可能影响航运、港口等相关A股板块</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>足金饰品报价首次达每克1100元</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>/article/7553215724735431206/</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>华商网</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>4小时前</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="n">
+        <v>45923.91048611111</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>黄金价格变动直接影响黄金概念股和珠宝首饰板块</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>数览“十四五”成绩单丨从“有学上”到“上好学” 教育强国建设按下“加速键”</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>/article/7553200840232813071/</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>东南网</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>5小时前</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="n">
+        <v>45923.91048611111</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>教育政策利好教育板块股票</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>俄外长与美国务卿将在联大期间会晤 讨论广泛议题</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>/article/7553045585729749514/</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>上观新闻</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>15小时前</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="n">
+        <v>45923.91048611111</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>国际关系变化可能影响地缘政治敏感板块</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>全市场唯一钢铁ETF(515210)近10日净流入超5.7亿元，机构：稳增长工作方案发布，钢铁受益于反内卷加速</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>/article/7553159640993759753/</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>每日经济新闻</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>8小时前</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="n">
+        <v>45923.91697916666</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>直接涉及A股钢铁行业ETF资金流动及政策影响</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>国债期货午盘集体下跌，30年期主力合约跌0.52%</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>/article/7553123078910280207/</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>每日经济新闻</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>10小时前</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="n">
+        <v>45923.91697916666</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>国债期货行情与A股市场资金面及情绪存在间接关联</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>国务院、中央军委公布《军用土地管理条例》</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>/article/7553207992057938473/</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>上观新闻</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>5小时前</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="n">
+        <v>45923.93126157407</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>政策法规发布可能影响军工、地产等相关板块上市公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>两岸统一白皮书来了，台湾人民关心的都在里面，这是一颗定心丸！</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>/video/7553139184194650634/</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>海边静听潮声</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>9小时前</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="n">
+        <v>45923.93126157407</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>两岸政策文件可能影响相关概念股和市场情绪</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>温州宏丰：目前VC均热板材料已应用在相关消费电子领域</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>/article/7553129514340041242/</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>每日经济新闻</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>10小时前</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="n">
+        <v>45923.93822916667</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>温州宏丰是A股上市公司，涉及新材料业务，与股市直接相关</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>平高电气：中标约13.69亿元国家电网项目</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>/article/7553222805806989870/</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>每日经济新闻</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>4小时前</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="n">
+        <v>45923.94513888889</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>涉及上市公司中标重大合同，直接影响股价</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>东方海洋：子公司取得医疗器械注册证</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>/article/7553213794105819663/</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>每日经济新闻</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>5小时前</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="n">
+        <v>45923.94513888889</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>上市公司子公司获重要资质，属于利好信息</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>两市融资余额增加191.85亿元</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>/article/7553081027640558123/</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>每日经济新闻</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>13小时前</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="n">
+        <v>45923.94513888889</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>直接反映A股市场资金动向的核心指标</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>约百种罕见病用药纳入医保</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>/article/7553102689584890411/</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>环球健康</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>12小时前</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="n">
+        <v>45923.95171296296</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>医保政策调整会影响医药板块上市公司业绩</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>打卡国境线、逛小城早市、荡高空秋千、乘矿车下井……美团旅行00后“2025国庆新玩法”前瞻</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>/article/7553176678550241818/</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>济南日报·爱济南</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>7小时前</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="n">
+        <v>45923.95171296296</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>涉及美团等上市公司业务动态，与旅游消费板块相关</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>ETF两市成交额超4000亿元</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>/article/7553168924704080423/</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>每日经济新闻</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>8小时前</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="n">
+        <v>45923.95171296296</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>直接反映A股市场交易情况和ETF产品表现</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>俄外长与美国务卿将在联大期间会晤 讨论广泛议题</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>/article/7553026099995755048/</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>每日经济新闻</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
         <is>
           <t>17小时前</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>2025-09-23 11:40:29</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>半导体设备企业业务进展影响相关板块</t>
+      <c r="E107" s="2" t="n">
+        <v>45923.95171296296</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>大国外交关系变化可能影响全球金融市场和A股市场情绪</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>理财公司加大力度发行含权理财，宁银理财成上市公司调研“劳模”</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>/article/7553237543702020627/</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>21世纪经济报道</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>3小时前</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="n">
+        <v>45923.95171296296</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>直接涉及理财产品发行和上市公司调研，与A股市场密切相关</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>这些企业，重点培育！</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>/article/7553167170897707572/</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>辽宁日报</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>8小时前</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="n">
+        <v>45923.95873842593</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>企业培育政策可能涉及上市公司或拟上市公司，与A股市场相关</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>中国—东盟人工智能出版传播创新发展中心首期成果推出</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>/article/7553088907504747008/</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>中国新闻出版广电报</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>13小时前</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="n">
+        <v>45923.95873842593</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>人工智能产业发展相关，可能涉及A股相关科技板块上市公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>参股摩尔线程概念股反复活跃 和而泰4天3板</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>/article/7553094205279617582/</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>每日经济新闻</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>13小时前</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="n">
+        <v>45923.96599537037</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>直接涉及A股上市公司和而泰的股价表现和概念股</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>中原农险十载农情伴客户，同启振兴共赢路</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>/article/7553212591997223466/</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>大象新闻</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>6小时前</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="n">
+        <v>45923.98642361111</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>农业保险业务发展与农业板块上市公司相关</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>商务部国际贸易谈判代表兼副部长李成钢会见美国中西部地区政商领袖代表团</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>/article/7553178137840927247/</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>澎湃新闻</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>8小时前</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="n">
+        <v>45923.98642361111</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>中美经贸往来可能影响外贸相关A股板块</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>中国农民丰收节丨田野披上“黄金甲” 每帧都是“好日子”</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>/article/7553254940492317223/</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>保定日报</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>3小时前</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="n">
+        <v>45923.98642361111</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>农业丰收可能影响农业相关上市公司业绩</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>巴比食品：两高管拟增持300万-450万元</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>/article/7553225355247567403/</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>每日经济新闻</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>5小时前</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="n">
+        <v>45923.99340277778</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>上市公司高管增持信息，直接涉及A股市场</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>保利发展：拟发行不超过150亿元公司债券</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>/article/7553243625245737513/</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>每日经济新闻</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>4小时前</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="n">
+        <v>45924.00035879629</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>公司债券发行涉及A股上市公司融资行为</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>徐直军谈华为AI：核心战略就是“超节点+集群”</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>/article/7553042733644907043/</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>21世纪经济报道</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>17小时前</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="n">
+        <v>45924.00035879629</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>华为产业链涉及多个A股上市公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>电影《刺杀小说家2》预售开启</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>/article/7553106613537489444/</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>大象新闻</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>13小时前</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="n">
+        <v>45924.00035879629</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>影视行业涉及A股文化传媒板块</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>活动预告｜【战略清析论坛】第22期：地缘政治视野下的中欧嬗变</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>/article/7553158527641829940/</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>清华战略安全研究中心</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>8小时前</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="n">
+        <v>45924.00773148148</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>地缘政治变化可能影响国际贸易和A股市场</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>多品牌“一口价黄金”即将涨价，有品牌24日将上调100元至500元</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>/article/7553241957858935332/</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>大众新闻•半岛都市报</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>4小时前</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="n">
+        <v>45924.00773148148</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>黄金价格上涨可能影响黄金概念股和A股市场</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>足金饰品报价首次达每克1100元</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>/article/7553205020108325427/</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>济南日报·爱济南</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>7小时前</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="n">
+        <v>45924.01417824074</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>黄金价格变动会影响黄金概念股和珠宝首饰板块股价</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>CPO等算力硬件股盘初活跃，中际旭创涨超8%</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>/article/7553092899433415177/</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>每日经济新闻</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>14小时前</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="n">
+        <v>45924.01417824074</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>直接报道A股市场算力硬件板块个股表现</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>18天直达欧洲！全球首条中欧北极集装箱快航正式通航</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>/article/7553094259692339727/</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>济南日报·爱济南</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>14小时前</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="n">
+        <v>45924.01417824074</v>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>航运物流新闻会影响港口航运板块上市公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>元鼎智能Aiper与全球最大泳池设备及户外生活用品经销商POOLCORP达成战略合作</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>/article/7553275069414343183/</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>雷峰网</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>3小时前</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="n">
+        <v>45924.0215625</v>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>涉及智能科技企业战略合作，可能对相关概念股产生影响</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>网信部门依法查处UC平台破坏网络生态案件</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>/article/7553209282267791881/</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>上观新闻</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>7小时前</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="n">
+        <v>45924.0215625</v>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>互联网平台监管事件，可能对相关互联网公司股价产生影响</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>君乐宝的 2 万亩 “试验”：用极致工业化，重构乳业逻辑</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>/article/7553093030703383079/</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>晚点LatePost</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>14小时前</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="n">
+        <v>45924.0284837963</v>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>君乐宝是乳制品行业重要企业，其产业布局和工业化发展对食品饮料板块及相关上市公司有直接影响</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>超越美国 “老登”后，50亿跨境大卖谈未来十年红利 ｜ Global AI  Booming</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>/article/7553264601702351412/</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>钛媒体APP</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>3小时前</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="n">
+        <v>45924.0284837963</v>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>涉及跨境电商和AI概念，与A股跨境电商、人工智能板块相关上市公司有关联</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>市场监管总局发布《重点排放单位碳计量审查规范》</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>/article/7553160954867974699/</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>同花顺财经</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>10小时前</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="n">
+        <v>45924.0284837963</v>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>碳计量政策直接影响环保、碳排放相关上市公司，对碳交易概念股有重要影响</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>27.98万起，全新问界M7正式上市！余承东：小订已破23万台！“华为系最便宜”车型小订突破16万台</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>/article/7553272064384238131/</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>每日经济新闻</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>3小时前</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="n">
+        <v>45924.03548611111</v>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>华为汽车产业链可能影响相关A股上市公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>罗永浩凌晨发文：将测评预制菜</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>/article/7553140587529847331/</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>浙江之声</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>12小时前</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="n">
+        <v>45924.03548611111</v>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>预制菜行业动态可能影响相关食品加工类A股</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>美团构建全链条消防安全体系 骑手保障成效显著事故降 25%</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>/article/7553179064992563727/</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>南充传媒集团</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>9小时前</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="n">
+        <v>45924.04234953703</v>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>美团是港股上市公司，但其业务动态可能影响中概股和A股市场情绪</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>东风华为两大掌门人首次会面合作战略再深化，猛士智能越野的天花板要来了？</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>/article/7553139320354325027/</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>长江财经智库</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>12小时前</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="n">
+        <v>45924.04234953703</v>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>东风汽车是A股上市公司，与华为的合作可能影响股价</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>BeBeBus上市首日涨近44%，创始人身家暴涨</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>/article/7553241648592650792/</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>36氪</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>5小时前</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="n">
+        <v>45924.04234953703</v>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>公司上市及股价表现，属于股市相关新闻</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>今日头条回应被约谈；罗永浩发布预制菜测试计划；雷军预热年度演讲 | 晚集</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>/article/7553271982834401832/</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>鞭牛士</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>3小时前</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="n">
+        <v>45924.04965277778</v>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>涉及今日头条（字节跳动概念股）、罗永浩预制菜（食品饮料概念）、雷军（小米集团相关），这些都可能对A股相关概念板块产生影响</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>iQOO 15将搭载2K三星珠峰屏：无偏光层，亮度更高功耗更低</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>/article/7553285030215270947/</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>环球Tech</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>3小时前</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="n">
+        <v>45924.04965277778</v>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>涉及消费电子和屏幕产业链，可能影响A股消费电子、显示面板等相关概念股</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>全智贤方否认中国代言被取消：预定活动和广告拍摄延期，但并不是取消；此前因台词争议遭强烈抵制</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>/article/7553113289287483958/</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>扬子晚报</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>14小时前</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="n">
+        <v>45924.04965277778</v>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>涉及明星代言争议，可能影响相关代言品牌的上市公司股价和市场表现</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>刚刚，金价创出今年“第36个新高”</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>/article/7553070142708531712/</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>华尔街见闻</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>17小时前</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="n">
+        <v>45924.0562037037</v>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>黄金价格波动可能影响A股黄金板块及相关概念股</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>雷军：小米17 Pro Max屏幕采用了革命性的技术</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>/article/7553109069838467634/</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>IT之家</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>14小时前</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="n">
+        <v>45924.0562037037</v>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>小米产业链技术突破可能带动A股相关供应链企业</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>科威特原油产能创十余年新高</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>/article/7553245313788625427/</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>上观新闻</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>5小时前</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="n">
+        <v>45924.0562037037</v>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>原油产能变化可能影响A股能源及化工板块</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>提质增效 稳中向好——中国建设银行发布2025年半年度经营业绩</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>/article/7553055489416839719/</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>21世纪经济报道</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>18小时前</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="n">
+        <v>45924.0562037037</v>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>银行股业绩直接影响A股金融板块</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>飞马国际：董事、总经理黄筱赟辞职</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>/article/7553195224081547811/</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>每日经济新闻</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>9小时前</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="n">
+        <v>45924.0562037037</v>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>上市公司高管变动属于A股公司公告事项</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>美国长债收益率“异常”上涨 “债券义警”拉响警报</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>/article/7553042713067733519/</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>21世纪经济报道</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>19小时前</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="n">
+        <v>45924.06315972222</v>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>美国债券市场波动可能影响全球资本市场情绪，间接关联A股</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>【产业互联网周报】  中国公有云上半年大模型调用量达536.7万亿Tokens；亚马逊云科技否认大中华区裁员；全球首个Agent交易市场MuleRun正式上线；美国据报将第四度延长TikTok不卖就禁期限；谷歌Gemini下载量超过ChatGPT</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>/article/7553101468534964751/</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>钛媒体APP</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>15小时前</t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="n">
+        <v>45924.06315972222</v>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>科技产业动态可能影响相关A股上市公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>湖北碳市场扩容有了时间表 明年酒店、商超、货运港口将入市</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>/article/7553234719350047272/</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>中国网湖北</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>6小时前</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="n">
+        <v>45924.06315972222</v>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>碳交易市场扩容涉及环保类A股上市公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>华为Mate 80系列“十大黑科技”曝光 含新一代红枫镜头</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>/article/7553104846397407790/</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>CNMO科技</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>15小时前</t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="n">
+        <v>45924.07013888889</v>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>华为产业链相关概念股可能受到新品技术发布的影响</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>机器人赛项融入应用场景丨技能照亮前程</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>/video/7553249969038197311/</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>大象新闻</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>5小时前</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="n">
+        <v>45924.07013888889</v>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>机器人技术发展可能影响相关智能制造板块股票</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>继50亿联手英特尔后 英伟达再斥千亿美元牵手OpenAI</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>/article/7553170609165877769/</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>中经TMT</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>11小时前</t>
+        </is>
+      </c>
+      <c r="E147" s="2" t="n">
+        <v>45924.07013888889</v>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>AI芯片巨头合作可能对A股人工智能和芯片板块产生重大影响</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>15条措施！山西七部门打出房地产新政“组合拳”</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>/article/7553175115337400872/</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>长治发布</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>10小时前</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="n">
+        <v>45924.07703703704</v>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>房地产政策可能影响房地产板块股票表现</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>河南微短剧审查开启“快进”模式！平原示范区高效服务助力行业发展</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>/article/7553089692808315427/</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>新乡日报</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>16小时前</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="n">
+        <v>45924.07703703704</v>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>影视文化行业政策可能影响相关传媒板块股票</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>河南省市场监管局召开全省食品安全突出问题专项整治专题调度会</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>/article/7553214073391858211/</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>大河健康报</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>8小时前</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="n">
+        <v>45924.08402777778</v>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>食品安全监管政策可能影响食品饮料行业上市公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>国内成品油价格按机制不作调整</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>/article/7553181596577219081/</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>青岛日报</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>10小时前</t>
+        </is>
+      </c>
+      <c r="E151" s="2" t="n">
+        <v>45924.08402777778</v>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>油价政策调整直接影响石油石化行业，对A股能源板块有重要影响</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>半年 8 款新车，大六座 SUV 的 “最卷之战” 即将上演</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>/article/7553253298770412075/</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>晚点LatePost</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>6小时前</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="n">
+        <v>45924.0909837963</v>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>汽车行业竞争可能影响相关汽车制造和零部件上市公司股价</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>我国充电桩总数突破1734万</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>/article/7553114125694435881/</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>大象新闻</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>15小时前</t>
+        </is>
+      </c>
+      <c r="E153" s="2" t="n">
+        <v>45924.0909837963</v>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>充电桩基础设施建设涉及新能源产业链，与A股新能源、充电桩概念股相关</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>港股收盘 | 港股三大指数高开低走，云栖大会明日开幕，市场预计阿里或提升Capex指引</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>/article/7553213800841871911/</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>每日经济新闻</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>8小时前</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="n">
+        <v>45924.0909837963</v>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>港股走势和阿里相关消息会对A股科技板块产生联动影响</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>上海建工盘中再度涨停：未持有宇树科技股份，黄金业务收入占比不足0.5%</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>/article/7553220899957178922/</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>澎湃新闻</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>8小时前</t>
+        </is>
+      </c>
+      <c r="E155" s="2" t="n">
+        <v>45924.09784722222</v>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>涉及A股上市公司股价异动及业务说明</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>日产汽车计划2028年前推ProPilot高阶版 对标特斯拉FSD</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>/article/7553125253192204826/</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>环球Tech</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>14小时前</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="n">
+        <v>45924.10482638889</v>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>汽车行业技术发展，可能影响新能源汽车和自动驾驶相关A股板块</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>突发：甲骨文CEO下台！和OpenAI签3000亿美元大单，或因路线斗争</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>/article/7553230639345762856/</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>新智元</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>8小时前</t>
+        </is>
+      </c>
+      <c r="E157" s="2" t="n">
+        <v>45924.11181712963</v>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>涉及科技巨头甲骨文和OpenAI的重大商业合作，可能影响相关科技板块股价</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>OpenAI走向“算力帝国”</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>/article/7552998930213028362/</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>虎嗅APP</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>23小时前</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="n">
+        <v>45924.11181712963</v>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>AI巨头发展动向可能影响科技股和AI概念股</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>余额宝降费！易方达、国新国证多只货币基金同步调整</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>/article/7553269913268372011/</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>每日经济新闻</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>5小时前</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="n">
+        <v>45924.1187037037</v>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>涉及货币基金费率调整，直接影响基金公司和相关金融板块股价</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>对话尼尔森IQ：新消费浪潮下中小企业要从渠道与消费者找突破口</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>/article/7553216973715391027/</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>21世纪经济报道</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>9小时前</t>
+        </is>
+      </c>
+      <c r="E160" s="2" t="n">
+        <v>45924.1187037037</v>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>消费行业分析，涉及中小企业发展策略，与消费板块上市公司相关</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>瑞银：维持对MSCI中国的超配观点，A50ETF（159601）逆势上行</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>/article/7553101901970129427/</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>每日经济新闻</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>16小时前</t>
+        </is>
+      </c>
+      <c r="E161" s="2" t="n">
+        <v>45924.1187037037</v>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>直接涉及A股市场投资策略和ETF基金表现，与A股高度相关</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>8月份全社会用电量再破万亿，同比增长5.0%</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>/article/7553194820345365019/</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>济南日报·爱济南</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>10小时前</t>
+        </is>
+      </c>
+      <c r="E162" s="2" t="n">
+        <v>45924.12564814815</v>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>宏观经济数据可能影响电力能源板块A股走势</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>网信部门依法查处UC平台破坏网络生态案件</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>/article/7553209186927034919/</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>大象新闻</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>10小时前</t>
+        </is>
+      </c>
+      <c r="E163" s="2" t="n">
+        <v>45924.13964120371</v>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>平台监管政策可能影响互联网板块上市公司股价</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>突发：甲骨文CEO下台，刚和OpenAI签下3000亿美元大单，或因路线斗争</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>/article/7553226203449016871/</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>36氪</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>9小时前</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="n">
+        <v>45924.13964120371</v>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>科技巨头重大人事变动和大额合作可能影响A股相关科技板块</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>鸿蒙“天工计划”启动：10亿资金资源，鸿蒙AI生态全速进击</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>/article/7553191802237403657/</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>环球Tech</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>11小时前</t>
+        </is>
+      </c>
+      <c r="E165" s="2" t="n">
+        <v>45924.14613425926</v>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>涉及鸿蒙生态和资金投入，可能影响相关科技板块上市公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>*ST星农：股东李伟红拟减持不超3%公司股份</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>/article/7553252932985881122/</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>每日经济新闻</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>7小时前</t>
+        </is>
+      </c>
+      <c r="E166" s="2" t="n">
+        <v>45924.14613425926</v>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>直接涉及上市公司股东减持事项，与A股市场密切相关</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>谁来给预制菜行业打破沉默的勇气？</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>/article/7553254886742262311/</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>上观新闻</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>7小时前</t>
+        </is>
+      </c>
+      <c r="E167" s="2" t="n">
+        <v>45924.15342592593</v>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>预制菜行业分析，涉及食品饮料板块上市公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>阿根廷宣布暂时取消农产品出口预扣税</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>/article/7553194449251762722/</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>东北新闻网</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>11小时前</t>
+        </is>
+      </c>
+      <c r="E168" s="2" t="n">
+        <v>45924.16005787037</v>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>农产品贸易政策变化可能影响农业、食品进口相关A股上市公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>中国银行山东省分行开启9月集中教育宣传周</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>/article/7553202386383274522/</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>大众新闻-大众日报</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>11小时前</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="n">
+        <v>45924.16005787037</v>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>银行金融机构活动，涉及银行板块A股</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>创新构建数据知识产权制度！浙江先行先试</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>/article/7553205973045805619/</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>今日浙江</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>10小时前</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="n">
+        <v>45924.16005787037</v>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>数据知识产权政策可能利好科技、知识产权相关A股</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>外媒：苹果折叠屏可能是iPhone Air三明治 明年问世</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>/article/7553053256441430591/</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>CNMO科技</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>20小时前</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="n">
+        <v>45924.16005787037</v>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>消费电子新品可能影响苹果产业链、消费电子相关A股</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>海南自贸港建设即将进入新阶段！</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>/article/7553196540887466511/</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>哈尔滨日报</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>11小时前</t>
+        </is>
+      </c>
+      <c r="E172" s="2" t="n">
+        <v>45924.16729166666</v>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>海南自贸港政策可能对区域经济及部分A股上市公司产生影响</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>波兰将重新开放与白俄罗斯的边境口岸！此前中欧班列中断，已有中国外贸商紧急改转海运</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>/article/7553295271602487817/</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>每日经济新闻</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>5小时前</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="n">
+        <v>45924.16729166666</v>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>中欧物流变化可能影响外贸相关A股企业</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>波兰边境将重新开放！出口欧洲的浙江外贸企业在思考，未来走里海还是走北极？</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>/article/7553299979310268991/</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>上观新闻</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>4小时前</t>
+        </is>
+      </c>
+      <c r="E174" s="2" t="n">
+        <v>45924.16729166666</v>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>国际贸易路线调整涉及外贸及航运类A股公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>“美国政府很可能10月1日关门，且持续很久”？这意味着10月“非农、CPI等数据延迟”，美联储只能“遵循9月计划”</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>/article/7553083323313095168/</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>华尔街见闻</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>19小时前</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="n">
+        <v>45924.18121527778</v>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>美国经济数据和货币政策变化对全球股市包括A股市场有重要影响</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>谷歌Gemini人工智能助手将登陆电视端 预计覆盖超3亿台设备</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>/article/7553125259013112358/</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>环球Tech</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>16小时前</t>
+        </is>
+      </c>
+      <c r="E176" s="2" t="n">
+        <v>45924.18121527778</v>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>人工智能技术进展可能影响A股相关科技板块和概念股</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>上海通报多校午餐发臭事件：涉事公司涉嫌瞒报 已被立案侦查</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>/article/7553266935715136019/</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>央视新闻</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>7小时前</t>
+        </is>
+      </c>
+      <c r="E177" s="2" t="n">
+        <v>45924.18121527778</v>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>涉及食品安全和上市公司监管问题，可能对相关食品、教育类上市公司产生影响</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>现货黄金涨0.36%，报3760.02美元/盎司，再创历史新高</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>/article/7553200381598138931/</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>每日经济新闻</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>11小时前</t>
+        </is>
+      </c>
+      <c r="E178" s="2" t="n">
+        <v>45924.18814814815</v>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>黄金价格波动可能影响A股贵金属板块</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>英伟达1000亿美元投OpenAI，美银：会大赚3-5倍</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>/article/7553257518248641063/</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>华尔街见闻</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>8小时前</t>
+        </is>
+      </c>
+      <c r="E179" s="2" t="n">
+        <v>45924.18814814815</v>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>科技巨头投资动向可能影响A股AI相关概念股</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>机器人分工协作还有机器狗巡检，未来“超级工厂”要来了</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>/article/7553313874260132379/</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>界面新闻</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>4小时前</t>
+        </is>
+      </c>
+      <c r="E180" s="2" t="n">
+        <v>45924.19483796296</v>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>涉及智能制造和机器人技术，可能影响相关A股上市公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>中央纪委国家监委公开通报</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>/article/7553257543276036650/</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>津云</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>8小时前</t>
+        </is>
+      </c>
+      <c r="E181" s="2" t="n">
+        <v>45924.20177083334</v>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>中纪委通报可能涉及官员违纪，若涉及金融监管或上市公司高管，可能对相关股票产生影响</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>厦门市住房和建设局党组成员、副局长苏青云接受纪律审查和监察调查</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>/article/7553103259914650112/</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>福建日报</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>18小时前</t>
+        </is>
+      </c>
+      <c r="E182" s="2" t="n">
+        <v>45924.20177083334</v>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>地方住建系统官员被查，可能影响当地房地产政策预期，间接影响A股地产板块</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>涉嫌严重违纪违法，朱超被查</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>/article/7553299913858220559/</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>南京广播电视台</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>5小时前</t>
+        </is>
+      </c>
+      <c r="E183" s="2" t="n">
+        <v>45924.20177083334</v>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>官员违纪被查新闻，若涉及经济领域或上市公司关联方，可能对市场情绪产生影响</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>战舰战机全开火了，美不宣而战，18国军方齐聚北京，拉解放军联手</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>/article/7553230371060597248/</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>吴学兰</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>10小时前</t>
+        </is>
+      </c>
+      <c r="E184" s="2" t="n">
+        <v>45924.20177083334</v>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>涉及地缘政治和军事动态，可能影响国防军工板块及市场风险偏好</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>特斯拉Model Y“廉价版”配置变化曝光 起售价20万元内？</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>/article/7553122902594290203/</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>CNMO科技</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>17小时前</t>
+        </is>
+      </c>
+      <c r="E185" s="2" t="n">
+        <v>45924.20900462963</v>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>特斯拉作为新能源汽车龙头企业，其产品定价策略会直接影响A股新能源汽车产业链相关股票</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>资金布局国产替代，半导体设备ETF（159516）连续3日净流入超10亿元，规模超40亿元居同类第一</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>/article/7553110176807666227/</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>每日经济新闻</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>18小时前</t>
+        </is>
+      </c>
+      <c r="E186" s="2" t="n">
+        <v>45924.20900462963</v>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>直接涉及A股ETF基金的资金流向和规模情况，与A股市场高度相关</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>电气设备板块局部活跃 特锐德涨超15%</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>/article/7553101942034022922/</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>每日经济新闻</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>18小时前</t>
+        </is>
+      </c>
+      <c r="E187" s="2" t="n">
+        <v>45924.20900462963</v>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>直接报道A股电气设备板块和具体个股表现，与A股密切相关</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>今日头条回应被约谈：成立专项工作小组，全面自查自纠，坚决整改存在的问题</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>/article/7553271234307981824/</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>北京青年报</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>7小时前</t>
+        </is>
+      </c>
+      <c r="E188" s="2" t="n">
+        <v>45924.20900462963</v>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>互联网平台监管新闻，可能影响相关中概股和A股互联网概念股</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>英伟达与OpenAI达成千亿美元级合作 共建AI基础设施集群</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>/article/7553125242902790656/</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>环球Tech</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>17小时前</t>
+        </is>
+      </c>
+      <c r="E189" s="2" t="n">
+        <v>45924.21592592593</v>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>涉及AI巨头合作，可能影响A股AI和算力相关板块</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>郑州将迎来第6座火车站！</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>/article/7543904162266743336/</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>大河报</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>08月29日</t>
+        </is>
+      </c>
+      <c r="E190" s="2" t="n">
+        <v>45924.21592592593</v>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>基础设施建设可能涉及A股建筑、铁路相关上市公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>卫星板块催化不断，相关主题指数近一年涨超70%</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>/article/7553197774670545427/</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>每日经济新闻</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>12小时前</t>
+        </is>
+      </c>
+      <c r="E191" s="2" t="n">
+        <v>45924.22289351852</v>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>直接涉及股市板块表现和指数涨幅，与A股高度相关</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>等不来DeepSeek-R2的246天：梁文锋的“三重困境”与“三重挑战”</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>/article/7553226438138004006/</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>钛媒体APP</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>11小时前</t>
+        </is>
+      </c>
+      <c r="E192" s="2" t="n">
+        <v>45924.23680555556</v>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>AI技术发展报道，可能影响科技类股票</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>我国核燃料元件制造分析领域首个国际标准成功立项</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>/article/7553090859204018722/</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>草原云·内蒙古新闻网</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>20小时前</t>
+        </is>
+      </c>
+      <c r="E193" s="2" t="n">
+        <v>45924.23680555556</v>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>核能行业标准进展，可能影响核电板块股票</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>11国谈判失败，中方发现“内鬼”，印度态度转向美国。</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>/video/7553221672385200674/</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>智勇双全花猫稳稳当当</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>11小时前</t>
+        </is>
+      </c>
+      <c r="E194" s="2" t="n">
+        <v>45924.23680555556</v>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>国际关系变化可能影响市场情绪和相关板块</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>中美通话，特朗普说了个重要信息！一起来听 听88</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>/video/7553145717133476403/</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>小历听歌</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>16小时前</t>
+        </is>
+      </c>
+      <c r="E195" s="2" t="n">
+        <v>45924.23680555556</v>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>中美高层对话可能对股市产生重要影响</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>金价，大涨！再创历史</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>/article/7553147914311254538/</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>济南日报·爱济南</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>16小时前</t>
+        </is>
+      </c>
+      <c r="E196" s="2" t="n">
+        <v>45924.24335648148</v>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>金价大涨直接影响黄金板块上市公司股价</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>世纪数码冲刺北交所上市 股权结构变动被问询</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>/article/7553275682491580968/</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>每日经济新闻</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>8小时前</t>
+        </is>
+      </c>
+      <c r="E197" s="2" t="n">
+        <v>45924.24335648148</v>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>直接涉及北交所上市公司IPO进程，与A股市场密切相关</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>新华鲜报丨高“含科量”！金融服务科技创新跑出“加速度”</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>/article/7553099588102750756/</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>东南网</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>19小时前</t>
+        </is>
+      </c>
+      <c r="E198" s="2" t="n">
+        <v>45924.25064814815</v>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>涉及金融服务科技创新，可能与A股金融科技板块相关</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>海南自贸港第一批31个封关项目全部建成｜活力中国调研行</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>/article/7553070059602690570/</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>21世纪经济报道</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>21小时前</t>
+        </is>
+      </c>
+      <c r="E199" s="2" t="n">
+        <v>45924.25064814815</v>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>海南自贸港建设可能影响区域经济及相关A股上市公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>靴子落地，欧盟对国林科技乙醛酸产品征收57.3%反倾销税，较初裁下调118个百分点</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>/article/7553300364196348426/</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>每日经济新闻</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>6小时前</t>
+        </is>
+      </c>
+      <c r="E200" s="2" t="n">
+        <v>45924.25064814815</v>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>直接影响上市公司国林科技的出口业务及股价表现</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>昊华科技：部分特气产品国内占有率达60% 正研制光刻用电子混配气产品</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>/article/7553108621010240039/</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>每日经济新闻</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>19小时前</t>
+        </is>
+      </c>
+      <c r="E201" s="2" t="n">
+        <v>45924.25725694445</v>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>昊华科技为A股上市公司，涉及公司业务和产品研发进展</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>福建舰电磁弹射宣传片震撼发布</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>/video/7553079232239288872/</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>大象新闻</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>21小时前</t>
+        </is>
+      </c>
+      <c r="E202" s="2" t="n">
+        <v>45924.25725694445</v>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>涉及军工装备，可能对相关A股军工板块产生影响</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>文化和旅游部通报第五批次文化和旅游领域暗访情况</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>/article/7553081631377867274/</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>华商网</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>21小时前</t>
+        </is>
+      </c>
+      <c r="E203" s="2" t="n">
+        <v>45924.25725694445</v>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>文旅行业监管信息，可能影响A股旅游、文化相关上市公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>顺鑫亮相第一届地理标志产品国际博览会！</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>/article/7553169783533928994/</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>北京青年报顺义新媒体</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>15小时前</t>
+        </is>
+      </c>
+      <c r="E204" s="2" t="n">
+        <v>45924.27120370371</v>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>顺鑫是A股上市公司顺鑫农业的简称，涉及上市公司动态</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>立讯精密：公司经营情况及内外部经营环境未发生重大变化</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>/article/7553242335175066155/</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>每日经济新闻</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>11小时前</t>
+        </is>
+      </c>
+      <c r="E205" s="2" t="n">
+        <v>45924.27120370371</v>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>立讯精密是A股上市公司，内容涉及公司经营情况公告</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>盛天网络：《真・三国无双天下》预计2026年上半年上线</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>/article/7553263368757559849/</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>每日经济新闻</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>9小时前</t>
+        </is>
+      </c>
+      <c r="E206" s="2" t="n">
+        <v>45924.27120370371</v>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>盛天网络是A股上市公司，涉及新产品发布计划</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>当 AI 从试点进入规模化，华为数字金融的长期选择</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>/article/7553280400261612041/</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>晚点LatePost</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>8小时前</t>
+        </is>
+      </c>
+      <c r="E207" s="2" t="n">
+        <v>45924.27810185185</v>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>涉及AI和数字金融发展，与科技股、金融科技板块相关</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>中部首座人形机器人训练场启用</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>/article/7553223087467921959/</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>河南日报</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>12小时前</t>
+        </is>
+      </c>
+      <c r="E208" s="2" t="n">
+        <v>45924.27810185185</v>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>机器人产业发展与人工智能、智能制造板块相关</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>福龙马：公司城市服务机器人尚处于起步拓展阶段</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>/article/7553241071095005715/</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>每日经济新闻</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>11小时前</t>
+        </is>
+      </c>
+      <c r="E209" s="2" t="n">
+        <v>45924.28501157407</v>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>涉及上市公司福龙马(603686)的业务发展情况，与A股直接相关</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>纽约期金突破3800美元/盎司，续刷历史新高</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>/article/7553203003180761651/</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>每日经济新闻</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>14小时前</t>
+        </is>
+      </c>
+      <c r="E210" s="2" t="n">
+        <v>45924.29230324074</v>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>黄金价格波动可能影响A股贵金属板块</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>资金持续流入红利类主题ETF标杆品种！红利ETF（510880）、红利低波ETF（512890）近三个交易日分别累计揽金7.1亿、2.9亿</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>/article/7553149354635313690/</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>每日经济新闻</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>17小时前</t>
+        </is>
+      </c>
+      <c r="E211" s="2" t="n">
+        <v>45924.29230324074</v>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>ETF资金流向直接反映A股市场投资动态</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>“中国版英伟达”摩尔线程周五才上会，A股“朋友圈”先炸开锅：和而泰4天3板，联美控股、初灵信息两连板</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>/article/7553205523995296299/</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>每日经济新闻</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>14小时前</t>
+        </is>
+      </c>
+      <c r="E212" s="2" t="n">
+        <v>45924.29927083333</v>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>直接提及A股上市公司股价表现，高度相关</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>美联储最新，事关降息！</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>/article/7553120029684941331/</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>每日经济新闻</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>19小时前</t>
+        </is>
+      </c>
+      <c r="E213" s="2" t="n">
+        <v>45924.3058912037</v>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>美联储降息政策会影响全球资本市场，包括A股市场</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>微海报丨河北年内月度进出口规模首超600亿元</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>/article/7553218626929656374/</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>河北新闻网</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>13小时前</t>
+        </is>
+      </c>
+      <c r="E214" s="2" t="n">
+        <v>45924.31278935185</v>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>进出口数据是宏观经济指标，会影响整体股市情绪和外贸相关板块</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>三个交易日涨近24%！立讯精密：不存在应披露而未披露的重大事项</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>/article/7553284289668874771/</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>澎湃新闻</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>9小时前</t>
+        </is>
+      </c>
+      <c r="E215" s="2" t="n">
+        <v>45924.31278935185</v>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>立讯精密是A股上市公司，涉及股价异动公告</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>中国东方资产管理股份有限公司广东省分公司    债权催收暨招商公告</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>/article/7553070417335763483/</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>南方日报</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>23小时前</t>
+        </is>
+      </c>
+      <c r="E216" s="2" t="n">
+        <v>45924.31278935185</v>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>资产管理公司业务涉及金融资产处置，可能影响相关金融板块</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>始祖鸟营销翻车，安踏撞上“烟花墙”</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>/article/7553247100927083023/</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>钛媒体APP</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>12小时前</t>
+        </is>
+      </c>
+      <c r="E217" s="2" t="n">
+        <v>45924.32008101852</v>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>安踏是A股上市公司，涉及品牌营销事件可能影响股价</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>2025国庆档新片预售票房破500万</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>/article/7553213782588129834/</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>每日经济新闻</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>14小时前</t>
+        </is>
+      </c>
+      <c r="E218" s="2" t="n">
+        <v>45924.32008101852</v>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>影视行业与A股影视公司相关，票房表现可能影响相关上市公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>2156万次！国内首个数字化医用耗材“云胶片”</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>/article/7553307671937270312/</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>上观新闻</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>8小时前</t>
+        </is>
+      </c>
+      <c r="E219" s="2" t="n">
+        <v>45924.32008101852</v>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>医疗科技创新可能涉及A股医疗器械板块</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>“十四五”期间我国金融事业取得新的重大成就</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>/article/7553091671584457256/</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>济南日报·爱济南</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>22小时前</t>
+        </is>
+      </c>
+      <c r="E220" s="2" t="n">
+        <v>45924.32675925926</v>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>金融事业发展与A股市场有间接关联，可能影响金融板块</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>2025欧亚经济论坛开幕 40个国家的政商学界代表共话发展</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>/article/7553323866362233371/</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>华商网</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>7小时前</t>
+        </is>
+      </c>
+      <c r="E221" s="2" t="n">
+        <v>45924.32675925926</v>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>国际经济论坛可能涉及经贸合作，对A股相关板块有潜在影响</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>阳光财险联合蚂蚁保推出一年期百万重疾险产品——“健康福·百万重疾(保1年)”</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>/article/7553182274330673718/</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>澎湃新闻</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>16小时前</t>
+        </is>
+      </c>
+      <c r="E222" s="2" t="n">
+        <v>45924.32675925926</v>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>保险行业新产品发布，涉及保险板块上市公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>专家解读：三型舰载机电磁弹射和阻拦着舰成功意义重大</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>/article/7553096841865347619/</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>济南日报·爱济南</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>21小时前</t>
+        </is>
+      </c>
+      <c r="E223" s="2" t="n">
+        <v>45924.32675925926</v>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>军工技术突破，可能影响军工板块上市公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>#河南那智工业机器人#河南工业机器人#郑州那智工业机器人#开封那智工业机器人#洛阳那智工业机器人</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>/video/7553406776582930996/</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>幸福就好</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>1小时前</t>
+        </is>
+      </c>
+      <c r="E224" s="2" t="n">
+        <v>45924.32675925926</v>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>工业机器人行业内容，可能涉及A股智能制造、机器人相关板块</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>火山引擎终于押中了MaaS的爆发</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>/article/7553247099479949858/</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>钛媒体APP</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>12小时前</t>
+        </is>
+      </c>
+      <c r="E225" s="2" t="n">
+        <v>45924.33400462963</v>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>MaaS(模型即服务)涉及科技和云计算领域，可能与相关A股科技板块有关联</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>AI穿越三千年，古诗词里的丰收“活”了！</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>/video/7553101130943824423/</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>大象新闻</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>22小时前</t>
+        </is>
+      </c>
+      <c r="E226" s="2" t="n">
+        <v>45924.34056712963</v>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>AI技术相关新闻可能影响科技板块股票</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>网信部门依法查处UC平台破坏网络生态案件</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>/article/7553209674162602506/</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>每日经济新闻</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>14小时前</t>
+        </is>
+      </c>
+      <c r="E227" s="2" t="n">
+        <v>45924.34056712963</v>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>平台监管新闻可能影响相关互联网上市公司股价</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>西方盟友集体倒戈！法德英加澳葡同时发声，美国中东霸权或要崩塌</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>/article/7553191490105737782/</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>加麻不加辣</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>15小时前</t>
+        </is>
+      </c>
+      <c r="E228" s="2" t="n">
+        <v>45924.34056712963</v>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>国际政治局势变化可能影响全球金融市场包括A股</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>市场中长期向好趋势已然确立，聚焦自由现金流ETF（159201）布局机会</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>/article/7553094189187793458/</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>每日经济新闻</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>22小时前</t>
+        </is>
+      </c>
+      <c r="E229" s="2" t="n">
+        <v>45924.34791666667</v>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>直接涉及A股ETF投资和市场趋势分析，与A股高度相关</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>多地明确！提前发工资</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>/article/7553207110092341794/</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>济南日报·爱济南</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>15小时前</t>
+        </is>
+      </c>
+      <c r="E230" s="2" t="n">
+        <v>45924.34791666667</v>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>工资发放政策可能影响消费板块和整体经济预期，间接影响A股</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>31省将陆续开启养老金重算补发，部分人能补发两笔钱，有2000元吗</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>/article/7553195081340142090/</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>崇信融媒</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>16小时前</t>
+        </is>
+      </c>
+      <c r="E231" s="2" t="n">
+        <v>45924.35447916666</v>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>养老金政策可能影响保险、银行等金融板块股价</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>心源性猝死可预防！胸科医院首日临床应用最新型除颤植入手术</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>/article/7553240730882294299/</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>上观新闻</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>13小时前</t>
+        </is>
+      </c>
+      <c r="E232" s="2" t="n">
+        <v>45924.35447916666</v>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>医疗新技术可能影响医疗器械相关上市公司股价</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>神州控股科捷发布供应链智能体“小金”，破解企业AI应用“最后一公里”难题</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>/article/7553165132122178063/</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>中经TMT</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>18小时前</t>
+        </is>
+      </c>
+      <c r="E233" s="2" t="n">
+        <v>45924.35447916666</v>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>上市公司神州控股的新产品发布直接影响公司股价</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>2025年空气净化器十大品牌：除甲醛效果测评与解析-权威实测TOP10！</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>/article/7553209589051753010/</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>大众网济宁</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>15小时前</t>
+        </is>
+      </c>
+      <c r="E234" s="2" t="n">
+        <v>45924.35447916666</v>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>家电行业品牌测评可能影响相关上市公司股价</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>滴滴包车“十一”大放价，领200元立减券优惠出发</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>/article/7553256975888106010/</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>三湘都市报</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>12小时前</t>
+        </is>
+      </c>
+      <c r="E235" s="2" t="n">
+        <v>45924.35447916666</v>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>滴滴出行的促销活动可能影响其股价表现</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>富煌钢构：与二十二冶集团签订战略合作协议</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>/article/7553202998978920975/</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>每日经济新闻</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>15小时前</t>
+        </is>
+      </c>
+      <c r="E236" s="2" t="n">
+        <v>45924.36180555556</v>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>上市公司富煌钢构的重大合作协议，直接影响A股市场</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>康惠制药：证券简称变更为“康惠股份”</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>/article/7553230437968101927/</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>每日经济新闻</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>14小时前</t>
+        </is>
+      </c>
+      <c r="E237" s="2" t="n">
+        <v>45924.36180555556</v>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>A股上市公司证券简称变更，属于直接的股市相关信息</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>股价两个半月火箭式涨超10倍！智元机器人取得上纬新材控制权</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>/article/7553257241688703534/</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>澎湃新闻</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>12小时前</t>
+        </is>
+      </c>
+      <c r="E238" s="2" t="n">
+        <v>45924.36835648148</v>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>涉及上市公司股价变动及控制权变更</t>
         </is>
       </c>
     </row>
